--- a/cypress/downloads/resultsApproval_MCP_NON_FO.xlsx
+++ b/cypress/downloads/resultsApproval_MCP_NON_FO.xlsx
@@ -418,7 +418,7 @@
         <v>Pass</v>
       </c>
       <c r="C2" t="str">
-        <v>2025-06-18T01:36:13.037Z</v>
+        <v>2026-03-06T00:06:29.574Z</v>
       </c>
     </row>
     <row r="3">
@@ -429,7 +429,7 @@
         <v>Pass</v>
       </c>
       <c r="C3" t="str">
-        <v>2025-06-18T01:36:13.037Z</v>
+        <v>2026-03-06T00:06:29.575Z</v>
       </c>
     </row>
     <row r="4">
@@ -440,7 +440,7 @@
         <v>Pass</v>
       </c>
       <c r="C4" t="str">
-        <v>2025-06-18T01:36:14.294Z</v>
+        <v>2026-03-06T00:06:31.164Z</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>Pass</v>
       </c>
       <c r="C5" t="str">
-        <v>2025-06-18T01:36:14.514Z</v>
+        <v>2026-03-06T00:06:31.397Z</v>
       </c>
     </row>
   </sheetData>

--- a/cypress/downloads/resultsApproval_MCP_NON_FO.xlsx
+++ b/cypress/downloads/resultsApproval_MCP_NON_FO.xlsx
@@ -418,7 +418,7 @@
         <v>Pass</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-03-06T00:06:29.574Z</v>
+        <v>2026-03-09T01:20:35.571Z</v>
       </c>
     </row>
     <row r="3">
@@ -429,7 +429,7 @@
         <v>Pass</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-03-06T00:06:29.575Z</v>
+        <v>2026-03-09T01:20:35.571Z</v>
       </c>
     </row>
     <row r="4">
@@ -440,7 +440,7 @@
         <v>Pass</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-03-06T00:06:31.164Z</v>
+        <v>2026-03-09T01:20:36.246Z</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>Pass</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-03-06T00:06:31.397Z</v>
+        <v>2026-03-09T01:20:36.486Z</v>
       </c>
     </row>
   </sheetData>
